--- a/JsonConverter/ExcelFiles/EnemyData.xlsx
+++ b/JsonConverter/ExcelFiles/EnemyData.xlsx
@@ -49,13 +49,13 @@
     <t>BaseHP</t>
   </si>
   <si>
-    <t>BaseATK</t>
-  </si>
-  <si>
-    <t>BaseDEF</t>
-  </si>
-  <si>
-    <t>AttackInterval</t>
+    <t>BaseAttack</t>
+  </si>
+  <si>
+    <t>BaseDefense</t>
+  </si>
+  <si>
+    <t>CoolDown</t>
   </si>
   <si>
     <t>SkillId</t>
@@ -258,7 +258,7 @@
       <name val="Malgun Gothic"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,6 +275,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9F2D0"/>
         <bgColor rgb="FFD9F2D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -386,6 +392,9 @@
     </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -689,13 +698,13 @@
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -703,172 +712,172 @@
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>500.0</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <v>50.0</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>20.0</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <v>1.5</v>
       </c>
-      <c r="G4" s="10"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>350.0</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>65.0</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>15.0</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>1.8</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>800.0</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <v>35.0</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>40.0</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="10">
         <v>2.0</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <v>1800.0</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="10">
         <v>80.0</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>45.0</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <v>1.6</v>
       </c>
-      <c r="G7" s="10"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>900.0</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <v>80.0</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <v>30.0</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="10">
         <v>1.5</v>
       </c>
-      <c r="G8" s="10"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>650.0</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="10">
         <v>105.0</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <v>22.0</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <v>1.8</v>
       </c>
-      <c r="G9" s="10"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <v>1200.0</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="10">
         <v>65.0</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <v>55.0</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="10">
         <v>2.0</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>3200.0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <v>120.0</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>60.0</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>1.5</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1"/>
